--- a/frontend/public/templates/每趟旅程範本.xlsx
+++ b/frontend/public/templates/每趟旅程範本.xlsx
@@ -599,7 +599,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="10" width="24" customWidth="1" style="0"/>
+    <col min="1" max="11" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,22 +640,27 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">航廈</t>
+          <t xml:space="preserve">出發航廈</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">抵達航廈</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">行李說明</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">備註</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1001"/>
+  <autoFilter ref="A1:K1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 A001 至 A9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"A"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
@@ -667,7 +672,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="8" width="24" customWidth="1" style="0"/>
+    <col min="1" max="11" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,37 +688,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">飯店圖片網址</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">入住日期</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入住時間</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">退房日期</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">退房時間</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">地址</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">地圖網址</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">電話</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">備註</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1001"/>
+  <autoFilter ref="A1:K1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/每趟旅程範本.xlsx
+++ b/frontend/public/templates/每趟旅程範本.xlsx
@@ -223,12 +223,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M1001"/>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="請選擇固定選項" error="請使用下拉選單" sqref="G2:G1001">
-      <formula1>"景點,餐飲,交通,住宿,自由活動,其他"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 A001 至 A9999 格式" sqref="K2:K1001">
       <formula1>OR(K2="",IFERROR(AND(EXACT(K2,"A"&amp;TEXT(VALUE(MID(K2,2,4)),"000")),VALUE(MID(K2,2,4))&gt;=1,VALUE(MID(K2,2,4))&lt;=9999),FALSE))</formula1>
@@ -672,7 +669,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="11" width="24" customWidth="1" style="0"/>
+    <col min="1" max="13" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,9 +728,19 @@
           <t xml:space="preserve">備註</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K1001"/>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">訂房網站網址</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">價格</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/每趟旅程範本.xlsx
+++ b/frontend/public/templates/每趟旅程範本.xlsx
@@ -669,7 +669,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="13" width="24" customWidth="1" style="0"/>
+    <col min="1" max="14" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -738,9 +738,14 @@
           <t xml:space="preserve">價格</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M1001"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副標題</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N1001"/>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"H"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/每趟旅程範本.xlsx
+++ b/frontend/public/templates/每趟旅程範本.xlsx
@@ -151,7 +151,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="13" width="24" customWidth="1" style="0"/>
+    <col min="1" max="14" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -220,9 +220,14 @@
           <t xml:space="preserve">排序</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M1001"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">內文</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N1001"/>
   <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>

--- a/frontend/public/templates/每趟旅程範本.xlsx
+++ b/frontend/public/templates/每趟旅程範本.xlsx
@@ -151,7 +151,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="14" width="24" customWidth="1" style="0"/>
+    <col min="1" max="15" width="24" customWidth="1" style="0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -225,10 +225,15 @@
           <t xml:space="preserve">內文</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:N1001"/>
-  <dataValidations count="3">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">類別</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1001"/>
+  <dataValidations count="4">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 I001 至 I9999 格式" sqref="A2:A1001">
       <formula1>OR(A2="",IFERROR(AND(EXACT(A2,"I"&amp;TEXT(VALUE(MID(A2,2,4)),"000")),VALUE(MID(A2,2,4))&gt;=1,VALUE(MID(A2,2,4))&lt;=9999),FALSE))</formula1>
     </dataValidation>
@@ -237,6 +242,9 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="ID 格式錯誤" error="請使用 H001 至 H9999 格式" sqref="L2:L1001">
       <formula1>OR(L2="",IFERROR(AND(EXACT(L2,"H"&amp;TEXT(VALUE(MID(L2,2,4)),"000")),VALUE(MID(L2,2,4))&gt;=1,VALUE(MID(L2,2,4))&lt;=9999),FALSE))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="請選擇固定選項" error="請使用下拉選單" sqref="O2:O1001">
+      <formula1>"未分類,三餐,活動,交通,購物"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
